--- a/t22.xlsx
+++ b/t22.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\we-compare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BE885E-B045-4ACC-BDFC-C94D31FDACF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C5370D-2D55-420E-A80B-C9F4C90CCE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
   <si>
     <t>convert(ResBuffer.proto, table_AllianceRegionNumPropMapConf, AllianceRegionNumPropMapConfData.pbin)</t>
   </si>
@@ -166,18 +166,6 @@
   </si>
   <si>
     <t>单人防御</t>
-  </si>
-  <si>
-    <t>Alliance_AllArms_AttackLmperialCity_Per</t>
-  </si>
-  <si>
-    <t>AllArms_AttackLmperialCity_Per</t>
-  </si>
-  <si>
-    <t>拆迁效率</t>
-  </si>
-  <si>
-    <t>MarchSpeed_ImperialCity</t>
   </si>
   <si>
     <t>Army_MarchingSpeed_Inc</t>
@@ -238,9 +226,6 @@
     <t>皇城区域剑士防御</t>
   </si>
   <si>
-    <t>Spearman_Atk_KingArea</t>
-  </si>
-  <si>
     <t>Spearman_Attack_Per</t>
   </si>
   <si>
@@ -290,6 +275,14 @@
   </si>
   <si>
     <t>皇城区域弓兵防御</t>
+  </si>
+  <si>
+    <t>修改源27行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除源15行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -700,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="52.75" customWidth="1"/>
@@ -972,16 +965,16 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -989,17 +982,17 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="5" t="s">
-        <v>50</v>
+      <c r="A16" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -1007,17 +1000,17 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="6" t="s">
-        <v>52</v>
+      <c r="A17" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -1026,16 +1019,16 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1043,17 +1036,17 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>56</v>
+      <c r="A19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1062,16 +1055,16 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -1080,16 +1073,16 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -1098,16 +1091,16 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -1115,53 +1108,53 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="4"/>
+      <c r="A23" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>65</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -1170,16 +1163,16 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="8" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -1188,16 +1181,16 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -1206,16 +1199,16 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -1224,16 +1217,16 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -1242,16 +1235,16 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -1260,16 +1253,16 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -1277,32 +1270,14 @@
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>87</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/t22.xlsx
+++ b/t22.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\we-compare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C5370D-2D55-420E-A80B-C9F4C90CCE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0015CF-F0FC-49A0-8526-58AA2FFC322B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5320" yWindow="1520" windowWidth="28930" windowHeight="17450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="86">
   <si>
     <t>convert(ResBuffer.proto, table_AllianceRegionNumPropMapConf, AllianceRegionNumPropMapConfData.pbin)</t>
   </si>
@@ -282,6 +282,10 @@
   </si>
   <si>
     <t>删除源15行</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入13行</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -376,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -400,6 +404,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="52.75" customWidth="1"/>
@@ -929,34 +936,28 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>43</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -965,16 +966,16 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -982,17 +983,17 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="6" t="s">
-        <v>48</v>
+      <c r="A16" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -1000,17 +1001,17 @@
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="5" t="s">
-        <v>49</v>
+      <c r="A17" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -1019,16 +1020,16 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1036,17 +1037,17 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>19</v>
+      <c r="A19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1055,16 +1056,16 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -1073,16 +1074,16 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -1091,16 +1092,16 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -1108,53 +1109,53 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="5"/>
+      <c r="A23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="4"/>
+      <c r="A24" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="5"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -1163,16 +1164,16 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="8" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -1181,16 +1182,16 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="8" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -1199,16 +1200,16 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -1217,16 +1218,16 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -1235,16 +1236,16 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -1253,16 +1254,16 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -1270,14 +1271,32 @@
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="A32" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
